--- a/Result/profitability/8080.xlsx
+++ b/Result/profitability/8080.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.05375000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>21.8275</v>
+        <v>26.265</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.135</v>
+        <v>0.14125</v>
       </c>
       <c r="N3" t="n">
-        <v>20.39875</v>
+        <v>26.32875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0.255</v>
+        <v>0.235</v>
       </c>
       <c r="N4" t="n">
-        <v>20.67625</v>
+        <v>24.62</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25125</v>
+        <v>0.2275</v>
       </c>
       <c r="N5" t="n">
-        <v>18.87375</v>
+        <v>23.075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.215</v>
+        <v>0.21625</v>
       </c>
       <c r="N6" t="n">
-        <v>17.82875</v>
+        <v>23.12375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.205</v>
+        <v>0.20875</v>
       </c>
       <c r="N7" t="n">
-        <v>17.37</v>
+        <v>21.72125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20375</v>
+        <v>0.195</v>
       </c>
       <c r="N8" t="n">
-        <v>15.665</v>
+        <v>16.41</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01499999999999998</v>
+        <v>0.015</v>
       </c>
       <c r="N11" t="n">
         <v>9.081250000000001</v>
@@ -2026,7 +2026,7 @@
         <v>0.19</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0975</v>
+        <v>-0.09749999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>8.45125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.75625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.959999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1175542406311636</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.357142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.458134490238611</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
